--- a/Cosas que llegan de mercado/2026/Periodo 1/nota 7.xlsx
+++ b/Cosas que llegan de mercado/2026/Periodo 1/nota 7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Motozom\Cosas que llegan de mercado\2026\Periodo 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C70E676-B16A-4870-8215-9E02B6633A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336C7F34-5079-4018-962F-9D70BB439FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>Cantidad</t>
   </si>
@@ -58,6 +58,12 @@
   </si>
   <si>
     <t>SIM LLEGO COMPLETO Y SIN DETALLES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SI LLEGO COMPLETO Y SIN DETALLES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SI LLEGO COMPLETO Y SIN  DETALLES </t>
   </si>
 </sst>
 </file>
@@ -936,7 +942,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I34" s="1">
         <v>1</v>
       </c>
@@ -947,6 +953,9 @@
         <f t="shared" ref="K34" si="1">I34*J34</f>
         <v>295</v>
       </c>
+      <c r="L34" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="49" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I49" s="1">
@@ -959,6 +968,9 @@
         <f t="shared" ref="K49" si="2">I49*J49</f>
         <v>293</v>
       </c>
+      <c r="L49" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="62" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I62" s="1">
@@ -975,7 +987,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I76" s="1">
         <v>1</v>
       </c>
@@ -985,6 +997,9 @@
       <c r="K76">
         <f t="shared" ref="K76" si="4">I76*J76</f>
         <v>849</v>
+      </c>
+      <c r="L76" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="95" spans="9:12" x14ac:dyDescent="0.25">
